--- a/backtest_runs/20260410_193731/by_symbol/CHAS/CHAS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/CHAS/CHAS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-2566.859999999999</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>102036.28</v>
@@ -679,7 +679,7 @@
         <v>-6395.640000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>96959.92</v>
@@ -817,7 +817,7 @@
         <v>-3283.859999999999</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>101319.28</v>
@@ -863,7 +863,7 @@
         <v>-3240.839999999997</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>98078.44</v>
@@ -1139,7 +1139,7 @@
         <v>-157.7399999999992</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>112504.48</v>
@@ -1231,7 +1231,7 @@
         <v>-4617.479999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>117064.6</v>
@@ -1277,7 +1277,7 @@
         <v>-7313.399999999991</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>109751.2</v>
@@ -1323,7 +1323,7 @@
         <v>-3040.080000000006</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>106711.12</v>
@@ -1369,7 +1369,7 @@
         <v>-57.35999999998859</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>106653.76</v>
@@ -1415,7 +1415,7 @@
         <v>-4158.600000000009</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>102495.16</v>
@@ -1461,7 +1461,7 @@
         <v>-3728.400000000002</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>98766.75999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-430.199999999996</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>98336.56</v>
@@ -1553,7 +1553,7 @@
         <v>-1018.140000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>97318.42</v>
@@ -1645,7 +1645,7 @@
         <v>-3556.319999999996</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>101319.28</v>
